--- a/diseases/d014/2010-2014.xlsx
+++ b/diseases/d014/2010-2014.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1509,11 +1509,11 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>7.398849328288879e-05</v>
+        <v>7.457622062629111e-05</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -4173,11 +4173,11 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>7.351586189943743e-05</v>
+        <v>7.412019330546414e-05</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -4321,11 +4321,11 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>7.301823768600205e-05</v>
+        <v>7.357160724533189e-05</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -6245,11 +6245,11 @@
         <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>0.0001450317867091508</v>
+        <v>0.0001462779573746032</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -13941,11 +13941,11 @@
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0.0001440972051156825</v>
+        <v>0.000145300262993476</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -15425,7 +15425,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -17053,7 +17053,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -17793,7 +17793,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -18533,7 +18533,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -19421,7 +19421,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -20161,7 +20161,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">

--- a/diseases/d014/2010-2014.xlsx
+++ b/diseases/d014/2010-2014.xlsx
@@ -776,6 +776,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6284,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6252,6 +6437,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6590,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6548,6 +6743,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6696,6 +6896,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7584,6 +7789,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8324,6 +8534,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9064,6 +9279,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9952,6 +10172,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10692,6 +10917,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11432,6 +11662,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12320,6 +12555,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13060,6 +13300,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13948,6 +14193,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14688,6 +14938,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15428,6 +15683,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16168,6 +16428,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17056,6 +17321,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17796,6 +18066,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18536,6 +18811,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19424,6 +19704,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20164,6 +20449,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21052,6 +21342,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21790,6 +22085,11 @@
       <c r="S144" t="inlineStr">
         <is>
           <t>nbs_computed</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">

--- a/diseases/d014/2010-2014.xlsx
+++ b/diseases/d014/2010-2014.xlsx
@@ -7049,28 +7049,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -7197,28 +7211,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -7345,28 +7373,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -7493,28 +7535,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -7641,28 +7697,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -7942,28 +8012,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -8090,28 +8174,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -8238,28 +8336,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -8386,28 +8498,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -8687,28 +8813,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -8835,28 +8975,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -8983,28 +9137,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -9131,28 +9299,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -9432,28 +9614,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -9580,28 +9776,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -9728,28 +9938,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -9876,28 +10100,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -10024,28 +10262,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -10325,28 +10577,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -10473,28 +10739,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -10621,28 +10901,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -10769,28 +11063,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -11070,28 +11378,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -11218,28 +11540,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -11366,28 +11702,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -11514,28 +11864,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -11815,28 +12179,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -11963,28 +12341,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -12111,28 +12503,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -12259,28 +12665,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -12407,28 +12827,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -12708,28 +13142,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -12856,28 +13304,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -13004,28 +13466,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -13152,28 +13628,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -13453,28 +13943,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -13601,28 +14105,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -13749,28 +14267,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -13897,28 +14429,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -14045,28 +14591,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -14346,28 +14906,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -14494,28 +15068,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -14642,28 +15230,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -14790,28 +15392,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -15091,28 +15707,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -15239,28 +15869,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -15387,28 +16031,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -15535,28 +16193,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -15836,28 +16508,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -15984,28 +16670,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -16132,28 +16832,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -16280,28 +16994,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -16581,28 +17309,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -16729,28 +17471,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -16877,28 +17633,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -17025,28 +17795,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -17173,28 +17957,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -17474,28 +18272,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -17622,28 +18434,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -17770,28 +18596,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -17918,28 +18758,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -18219,28 +19073,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -18367,28 +19235,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -18515,28 +19397,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -18663,28 +19559,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -18964,28 +19874,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -19112,28 +20036,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -19260,28 +20198,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -19408,28 +20360,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -19556,28 +20522,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -19857,28 +20837,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -20005,28 +20999,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -20153,28 +21161,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -20301,28 +21323,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -20602,28 +21638,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -20750,28 +21800,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -20898,28 +21962,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
@@ -21046,28 +22124,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -21194,28 +22286,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -21495,28 +22601,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
@@ -21643,28 +22763,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -21791,28 +22925,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -21939,28 +23087,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
@@ -22240,28 +23402,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
@@ -22388,28 +23564,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
@@ -22536,28 +23726,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
@@ -22684,28 +23888,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
+        </is>
+      </c>
       <c r="AT148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">

--- a/diseases/d014/2010-2014.xlsx
+++ b/diseases/d014/2010-2014.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -924,11 +909,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -941,22 +921,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1077,11 +1047,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1094,22 +1059,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1230,11 +1185,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1247,22 +1197,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1383,11 +1323,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1400,22 +1335,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1536,11 +1461,6 @@
       <c r="R7" t="n">
         <v>7.457622062629111e-05</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1553,22 +1473,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1689,11 +1599,6 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1706,22 +1611,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1842,11 +1737,6 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1859,22 +1749,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1995,11 +1875,6 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2012,22 +1887,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2148,11 +2013,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2165,22 +2025,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2301,11 +2151,6 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2318,22 +2163,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2454,11 +2289,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2471,22 +2301,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2607,11 +2427,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2624,22 +2439,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2760,11 +2565,6 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2777,22 +2577,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2913,11 +2703,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2930,22 +2715,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3066,11 +2841,6 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3083,22 +2853,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3219,11 +2979,6 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3236,22 +2991,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3372,11 +3117,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3389,22 +3129,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3525,11 +3255,6 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3542,22 +3267,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3678,11 +3393,6 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3695,22 +3405,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3831,11 +3531,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3848,22 +3543,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3984,11 +3669,6 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4001,22 +3681,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4137,11 +3807,6 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4154,22 +3819,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4290,11 +3945,6 @@
       <c r="R25" t="n">
         <v>7.412019330546414e-05</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4307,22 +3957,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4443,11 +4083,6 @@
       <c r="R26" t="n">
         <v>7.357160724533189e-05</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4460,22 +4095,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4596,11 +4221,6 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4613,22 +4233,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4749,11 +4359,6 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4766,22 +4371,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4902,11 +4497,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4919,22 +4509,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5055,11 +4635,6 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5072,22 +4647,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5208,11 +4773,6 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5225,22 +4785,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5361,11 +4911,6 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5378,22 +4923,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5514,11 +5049,6 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5531,22 +5061,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5667,11 +5187,6 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5684,22 +5199,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5820,11 +5325,6 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5837,22 +5337,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5973,11 +5463,6 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5990,22 +5475,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6126,11 +5601,6 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6143,22 +5613,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6279,11 +5739,6 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6296,22 +5751,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6432,11 +5877,6 @@
       <c r="R39" t="n">
         <v>0.0001462779573746032</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6449,22 +5889,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6585,11 +6015,6 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6602,22 +6027,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6738,11 +6153,6 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6755,22 +6165,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6891,11 +6291,6 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6908,22 +6303,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7854,11 +7239,6 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7871,22 +7251,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8655,11 +8025,6 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8672,22 +8037,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -9456,11 +8811,6 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9473,22 +8823,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -10419,11 +9759,6 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10436,22 +9771,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -11220,11 +10545,6 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11237,22 +10557,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -12021,11 +11331,6 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12038,22 +11343,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -12984,11 +12279,6 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13001,22 +12291,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -13785,11 +13065,6 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13802,22 +13077,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -14748,11 +14013,6 @@
       <c r="R91" t="n">
         <v>0.000145300262993476</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14765,22 +14025,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -15549,11 +14799,6 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15566,22 +14811,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -16350,11 +15585,6 @@
       <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16367,22 +15597,12 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -17151,11 +16371,6 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17168,22 +16383,12 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -18114,11 +17319,6 @@
       <c r="R112" t="n">
         <v>0</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18131,22 +17331,12 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -18915,11 +18105,6 @@
       <c r="R117" t="n">
         <v>0</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18932,22 +18117,12 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -19716,11 +18891,6 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19733,22 +18903,12 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -20679,11 +19839,6 @@
       <c r="R128" t="n">
         <v>0</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20696,22 +19851,12 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -21480,11 +20625,6 @@
       <c r="R133" t="n">
         <v>0</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21497,22 +20637,12 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -22443,11 +21573,6 @@
       <c r="R139" t="n">
         <v>0</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22460,22 +21585,12 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -23244,11 +22359,6 @@
       <c r="R144" t="n">
         <v>0</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23261,22 +22371,12 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>

--- a/diseases/d014/2010-2014.xlsx
+++ b/diseases/d014/2010-2014.xlsx
@@ -6423,17 +6423,15 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -6441,7 +6439,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -6451,12 +6449,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -6466,11 +6459,6 @@
       </c>
       <c r="AT43" t="n">
         <v>1</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6585,17 +6573,15 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -6603,7 +6589,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6613,12 +6599,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -6628,11 +6609,6 @@
       </c>
       <c r="AT44" t="n">
         <v>1</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6747,17 +6723,15 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -6765,7 +6739,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6775,12 +6749,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -6790,11 +6759,6 @@
       </c>
       <c r="AT45" t="n">
         <v>1</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -6909,17 +6873,15 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -6927,7 +6889,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6937,12 +6899,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
@@ -6952,11 +6909,6 @@
       </c>
       <c r="AT46" t="n">
         <v>1</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7071,17 +7023,15 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -7089,7 +7039,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -7099,12 +7049,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
@@ -7114,11 +7059,6 @@
       </c>
       <c r="AT47" t="n">
         <v>1</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7371,17 +7311,15 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -7389,7 +7327,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -7399,12 +7337,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
@@ -7414,11 +7347,6 @@
       </c>
       <c r="AT49" t="n">
         <v>1</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7533,17 +7461,15 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -7551,7 +7477,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -7561,12 +7487,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
@@ -7576,11 +7497,6 @@
       </c>
       <c r="AT50" t="n">
         <v>1</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7695,17 +7611,15 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -7713,7 +7627,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -7723,12 +7637,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
@@ -7738,11 +7647,6 @@
       </c>
       <c r="AT51" t="n">
         <v>1</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7857,17 +7761,15 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -7875,7 +7777,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7885,12 +7787,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
@@ -7900,11 +7797,6 @@
       </c>
       <c r="AT52" t="n">
         <v>1</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8157,17 +8049,15 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -8175,7 +8065,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -8185,12 +8075,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ54" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
@@ -8200,11 +8085,6 @@
       </c>
       <c r="AT54" t="n">
         <v>1</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8319,17 +8199,15 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -8337,7 +8215,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -8347,12 +8225,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -8362,11 +8235,6 @@
       </c>
       <c r="AT55" t="n">
         <v>1</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8481,17 +8349,15 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -8499,7 +8365,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -8509,12 +8375,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
@@ -8524,11 +8385,6 @@
       </c>
       <c r="AT56" t="n">
         <v>1</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8643,17 +8499,15 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -8661,7 +8515,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -8671,12 +8525,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
@@ -8686,11 +8535,6 @@
       </c>
       <c r="AT57" t="n">
         <v>1</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8943,17 +8787,15 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -8961,7 +8803,7 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -8971,12 +8813,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
@@ -8986,11 +8823,6 @@
       </c>
       <c r="AT59" t="n">
         <v>1</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9105,17 +8937,15 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U60" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -9123,7 +8953,7 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -9133,12 +8963,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
@@ -9148,11 +8973,6 @@
       </c>
       <c r="AT60" t="n">
         <v>1</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9267,17 +9087,15 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -9285,7 +9103,7 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -9295,12 +9113,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ61" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
@@ -9310,11 +9123,6 @@
       </c>
       <c r="AT61" t="n">
         <v>1</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9429,17 +9237,15 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -9447,7 +9253,7 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -9457,12 +9263,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
@@ -9472,11 +9273,6 @@
       </c>
       <c r="AT62" t="n">
         <v>1</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9591,17 +9387,15 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U63" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -9609,7 +9403,7 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -9619,12 +9413,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ63" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
@@ -9634,11 +9423,6 @@
       </c>
       <c r="AT63" t="n">
         <v>1</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9891,17 +9675,15 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -9909,7 +9691,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -9919,12 +9701,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ65" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
@@ -9934,11 +9711,6 @@
       </c>
       <c r="AT65" t="n">
         <v>1</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10053,17 +9825,15 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U66" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -10071,7 +9841,7 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10081,12 +9851,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
@@ -10096,11 +9861,6 @@
       </c>
       <c r="AT66" t="n">
         <v>1</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10215,17 +9975,15 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -10233,7 +9991,7 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -10243,12 +10001,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
@@ -10258,11 +10011,6 @@
       </c>
       <c r="AT67" t="n">
         <v>1</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10377,17 +10125,15 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U68" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -10395,7 +10141,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -10405,12 +10151,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
@@ -10420,11 +10161,6 @@
       </c>
       <c r="AT68" t="n">
         <v>1</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10677,17 +10413,15 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U70" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -10695,7 +10429,7 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -10705,12 +10439,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
@@ -10720,11 +10449,6 @@
       </c>
       <c r="AT70" t="n">
         <v>1</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -10839,17 +10563,15 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -10857,7 +10579,7 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -10867,12 +10589,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
@@ -10882,11 +10599,6 @@
       </c>
       <c r="AT71" t="n">
         <v>1</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11001,17 +10713,15 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U72" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -11019,7 +10729,7 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -11029,12 +10739,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
@@ -11044,11 +10749,6 @@
       </c>
       <c r="AT72" t="n">
         <v>1</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11163,17 +10863,15 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -11181,7 +10879,7 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -11191,12 +10889,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
@@ -11206,11 +10899,6 @@
       </c>
       <c r="AT73" t="n">
         <v>1</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11463,17 +11151,15 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U75" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -11481,7 +11167,7 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -11491,12 +11177,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
@@ -11506,11 +11187,6 @@
       </c>
       <c r="AT75" t="n">
         <v>1</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11625,17 +11301,15 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -11643,7 +11317,7 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -11653,12 +11327,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
@@ -11668,11 +11337,6 @@
       </c>
       <c r="AT76" t="n">
         <v>1</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -11787,17 +11451,15 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -11805,7 +11467,7 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -11815,12 +11477,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
@@ -11830,11 +11487,6 @@
       </c>
       <c r="AT77" t="n">
         <v>1</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11949,17 +11601,15 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U78" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -11967,7 +11617,7 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -11977,12 +11627,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
@@ -11992,11 +11637,6 @@
       </c>
       <c r="AT78" t="n">
         <v>1</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12111,17 +11751,15 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U79" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -12129,7 +11767,7 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -12139,12 +11777,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
@@ -12154,11 +11787,6 @@
       </c>
       <c r="AT79" t="n">
         <v>1</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12411,17 +12039,15 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U81" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -12429,7 +12055,7 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -12439,12 +12065,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
@@ -12454,11 +12075,6 @@
       </c>
       <c r="AT81" t="n">
         <v>1</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12573,17 +12189,15 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -12591,7 +12205,7 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -12601,12 +12215,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
@@ -12616,11 +12225,6 @@
       </c>
       <c r="AT82" t="n">
         <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12735,17 +12339,15 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -12753,7 +12355,7 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -12763,12 +12365,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
@@ -12778,11 +12375,6 @@
       </c>
       <c r="AT83" t="n">
         <v>1</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12897,17 +12489,15 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U84" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -12915,7 +12505,7 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -12925,12 +12515,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
@@ -12940,11 +12525,6 @@
       </c>
       <c r="AT84" t="n">
         <v>1</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13197,17 +12777,15 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U86" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -13215,7 +12793,7 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -13225,12 +12803,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
@@ -13240,11 +12813,6 @@
       </c>
       <c r="AT86" t="n">
         <v>1</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13359,17 +12927,15 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -13377,7 +12943,7 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -13387,12 +12953,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
@@ -13402,11 +12963,6 @@
       </c>
       <c r="AT87" t="n">
         <v>1</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13521,17 +13077,15 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -13539,7 +13093,7 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -13549,12 +13103,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
@@ -13564,11 +13113,6 @@
       </c>
       <c r="AT88" t="n">
         <v>1</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13683,17 +13227,15 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -13701,7 +13243,7 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -13711,12 +13253,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
@@ -13726,11 +13263,6 @@
       </c>
       <c r="AT89" t="n">
         <v>1</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -13845,17 +13377,15 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U90" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -13863,7 +13393,7 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -13873,12 +13403,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
@@ -13888,11 +13413,6 @@
       </c>
       <c r="AT90" t="n">
         <v>1</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14145,17 +13665,15 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U92" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -14163,7 +13681,7 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -14173,12 +13691,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
@@ -14188,11 +13701,6 @@
       </c>
       <c r="AT92" t="n">
         <v>1</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14307,17 +13815,15 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -14325,7 +13831,7 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -14335,12 +13841,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
@@ -14350,11 +13851,6 @@
       </c>
       <c r="AT93" t="n">
         <v>1</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14469,17 +13965,15 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U94" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -14487,7 +13981,7 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -14497,12 +13991,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
@@ -14512,11 +14001,6 @@
       </c>
       <c r="AT94" t="n">
         <v>1</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14631,17 +14115,15 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -14649,7 +14131,7 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -14659,12 +14141,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
@@ -14674,11 +14151,6 @@
       </c>
       <c r="AT95" t="n">
         <v>1</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14931,17 +14403,15 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -14949,7 +14419,7 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -14959,12 +14429,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
@@ -14974,11 +14439,6 @@
       </c>
       <c r="AT97" t="n">
         <v>1</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15093,17 +14553,15 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -15111,7 +14569,7 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -15121,12 +14579,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
@@ -15136,11 +14589,6 @@
       </c>
       <c r="AT98" t="n">
         <v>1</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15255,17 +14703,15 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U99" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -15273,7 +14719,7 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -15283,12 +14729,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
@@ -15298,11 +14739,6 @@
       </c>
       <c r="AT99" t="n">
         <v>1</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -15417,17 +14853,15 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -15435,7 +14869,7 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -15445,12 +14879,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
@@ -15460,11 +14889,6 @@
       </c>
       <c r="AT100" t="n">
         <v>1</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -15717,17 +15141,15 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -15735,7 +15157,7 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -15745,12 +15167,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
@@ -15760,11 +15177,6 @@
       </c>
       <c r="AT102" t="n">
         <v>1</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -15879,17 +15291,15 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -15897,7 +15307,7 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -15907,12 +15317,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
@@ -15922,11 +15327,6 @@
       </c>
       <c r="AT103" t="n">
         <v>1</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -16041,17 +15441,15 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -16059,7 +15457,7 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -16069,12 +15467,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
@@ -16084,11 +15477,6 @@
       </c>
       <c r="AT104" t="n">
         <v>1</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -16203,17 +15591,15 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -16221,7 +15607,7 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -16231,12 +15617,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
@@ -16246,11 +15627,6 @@
       </c>
       <c r="AT105" t="n">
         <v>1</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -16503,17 +15879,15 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -16521,7 +15895,7 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -16531,12 +15905,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
@@ -16546,11 +15915,6 @@
       </c>
       <c r="AT107" t="n">
         <v>1</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -16665,17 +16029,15 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -16683,7 +16045,7 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -16693,12 +16055,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
@@ -16708,11 +16065,6 @@
       </c>
       <c r="AT108" t="n">
         <v>1</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -16827,17 +16179,15 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -16845,7 +16195,7 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -16855,12 +16205,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
@@ -16870,11 +16215,6 @@
       </c>
       <c r="AT109" t="n">
         <v>1</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -16989,17 +16329,15 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -17007,7 +16345,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -17017,12 +16355,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
@@ -17032,11 +16365,6 @@
       </c>
       <c r="AT110" t="n">
         <v>1</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -17151,17 +16479,15 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -17169,7 +16495,7 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -17179,12 +16505,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
@@ -17194,11 +16515,6 @@
       </c>
       <c r="AT111" t="n">
         <v>1</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17451,17 +16767,15 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -17469,7 +16783,7 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -17479,12 +16793,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
@@ -17494,11 +16803,6 @@
       </c>
       <c r="AT113" t="n">
         <v>1</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -17613,17 +16917,15 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -17631,7 +16933,7 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -17641,12 +16943,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
@@ -17656,11 +16953,6 @@
       </c>
       <c r="AT114" t="n">
         <v>1</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -17775,17 +17067,15 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -17793,7 +17083,7 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -17803,12 +17093,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -17818,11 +17103,6 @@
       </c>
       <c r="AT115" t="n">
         <v>1</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -17937,17 +17217,15 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -17955,7 +17233,7 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -17965,12 +17243,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
@@ -17980,11 +17253,6 @@
       </c>
       <c r="AT116" t="n">
         <v>1</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -18237,17 +17505,15 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -18255,7 +17521,7 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -18265,12 +17531,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
@@ -18280,11 +17541,6 @@
       </c>
       <c r="AT118" t="n">
         <v>1</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -18399,17 +17655,15 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -18417,7 +17671,7 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -18427,12 +17681,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
@@ -18442,11 +17691,6 @@
       </c>
       <c r="AT119" t="n">
         <v>1</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -18561,17 +17805,15 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -18579,7 +17821,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -18589,12 +17831,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
@@ -18604,11 +17841,6 @@
       </c>
       <c r="AT120" t="n">
         <v>1</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -18723,17 +17955,15 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -18741,7 +17971,7 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -18751,12 +17981,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
@@ -18766,11 +17991,6 @@
       </c>
       <c r="AT121" t="n">
         <v>1</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -19023,17 +18243,15 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U123" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -19041,7 +18259,7 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -19051,12 +18269,7 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
@@ -19066,11 +18279,6 @@
       </c>
       <c r="AT123" t="n">
         <v>1</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -19185,17 +18393,15 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U124" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -19203,7 +18409,7 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -19213,12 +18419,7 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
@@ -19228,11 +18429,6 @@
       </c>
       <c r="AT124" t="n">
         <v>1</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -19347,17 +18543,15 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -19365,7 +18559,7 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -19375,12 +18569,7 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
@@ -19390,11 +18579,6 @@
       </c>
       <c r="AT125" t="n">
         <v>1</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -19509,17 +18693,15 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
       <c r="Q126" t="n">
         <v>0</v>
       </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -19527,7 +18709,7 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -19537,12 +18719,7 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
@@ -19552,11 +18729,6 @@
       </c>
       <c r="AT126" t="n">
         <v>1</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -19671,17 +18843,15 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U127" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -19689,7 +18859,7 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -19699,12 +18869,7 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
@@ -19714,11 +18879,6 @@
       </c>
       <c r="AT127" t="n">
         <v>1</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -19971,17 +19131,15 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
       <c r="Q129" t="n">
         <v>0</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U129" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -19989,7 +19147,7 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -19999,12 +19157,7 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ129" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
@@ -20014,11 +19167,6 @@
       </c>
       <c r="AT129" t="n">
         <v>1</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -20133,17 +19281,15 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -20151,7 +19297,7 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -20161,12 +19307,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ130" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
@@ -20176,11 +19317,6 @@
       </c>
       <c r="AT130" t="n">
         <v>1</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -20295,17 +19431,15 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U131" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -20313,7 +19447,7 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -20323,12 +19457,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
@@ -20338,11 +19467,6 @@
       </c>
       <c r="AT131" t="n">
         <v>1</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -20457,17 +19581,15 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U132" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -20475,7 +19597,7 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -20485,12 +19607,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
@@ -20500,11 +19617,6 @@
       </c>
       <c r="AT132" t="n">
         <v>1</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -20757,17 +19869,15 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U134" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -20775,7 +19885,7 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -20785,12 +19895,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
@@ -20800,11 +19905,6 @@
       </c>
       <c r="AT134" t="n">
         <v>1</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -20919,17 +20019,15 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U135" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -20937,7 +20035,7 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -20947,12 +20045,7 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
@@ -20962,11 +20055,6 @@
       </c>
       <c r="AT135" t="n">
         <v>1</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -21081,17 +20169,15 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U136" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -21099,7 +20185,7 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -21109,12 +20195,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
@@ -21124,11 +20205,6 @@
       </c>
       <c r="AT136" t="n">
         <v>1</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -21243,17 +20319,15 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U137" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -21261,7 +20335,7 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -21271,12 +20345,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
@@ -21286,11 +20355,6 @@
       </c>
       <c r="AT137" t="n">
         <v>1</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -21405,17 +20469,15 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -21423,7 +20485,7 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -21433,12 +20495,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
@@ -21448,11 +20505,6 @@
       </c>
       <c r="AT138" t="n">
         <v>1</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -21705,17 +20757,15 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U140" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -21723,7 +20773,7 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -21733,12 +20783,7 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
@@ -21748,11 +20793,6 @@
       </c>
       <c r="AT140" t="n">
         <v>1</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -21867,17 +20907,15 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U141" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -21885,7 +20923,7 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -21895,12 +20933,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
@@ -21910,11 +20943,6 @@
       </c>
       <c r="AT141" t="n">
         <v>1</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -22029,17 +21057,15 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
       <c r="Q142" t="n">
         <v>0</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U142" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -22047,7 +21073,7 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -22057,12 +21083,7 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
@@ -22072,11 +21093,6 @@
       </c>
       <c r="AT142" t="n">
         <v>1</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -22191,17 +21207,15 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U143" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -22209,7 +21223,7 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -22219,12 +21233,7 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
@@ -22234,11 +21243,6 @@
       </c>
       <c r="AT143" t="n">
         <v>1</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -22491,17 +21495,15 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
       <c r="Q145" t="n">
         <v>0</v>
       </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U145" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -22509,7 +21511,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -22519,12 +21521,7 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ145" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
@@ -22534,11 +21531,6 @@
       </c>
       <c r="AT145" t="n">
         <v>1</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -22653,17 +21645,15 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
       <c r="Q146" t="n">
         <v>0</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U146" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -22671,7 +21661,7 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -22681,12 +21671,7 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
@@ -22696,11 +21681,6 @@
       </c>
       <c r="AT146" t="n">
         <v>1</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -22815,17 +21795,15 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
       <c r="Q147" t="n">
         <v>0</v>
       </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -22833,7 +21811,7 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -22843,12 +21821,7 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
@@ -22858,11 +21831,6 @@
       </c>
       <c r="AT147" t="n">
         <v>1</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -22977,17 +21945,15 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U148" t="inlineStr">
         <is>
           <t>HOLD_JP_e82ee0abd1605c338e084bcf6bf9</t>
@@ -22995,7 +21961,7 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -23005,12 +21971,7 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ148" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
@@ -23020,11 +21981,6 @@
       </c>
       <c r="AT148" t="n">
         <v>1</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
